--- a/output_files/payment sheet.xlsx
+++ b/output_files/payment sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="65">
   <si>
     <t>MID_WID</t>
   </si>
@@ -61,18 +61,21 @@
     <t>1139089</t>
   </si>
   <si>
+    <t>1181484_925160</t>
+  </si>
+  <si>
     <t>1182161</t>
   </si>
   <si>
-    <t>1183547</t>
-  </si>
-  <si>
     <t>1190435</t>
   </si>
   <si>
     <t>1220362</t>
   </si>
   <si>
+    <t>1233229</t>
+  </si>
+  <si>
     <t>1327789</t>
   </si>
   <si>
@@ -88,9 +91,15 @@
     <t>1530557_950125</t>
   </si>
   <si>
+    <t>1530557_950156</t>
+  </si>
+  <si>
     <t>1530559_950162</t>
   </si>
   <si>
+    <t>1530591</t>
+  </si>
+  <si>
     <t>279075_910640</t>
   </si>
   <si>
@@ -106,18 +115,21 @@
     <t>Euronet</t>
   </si>
   <si>
+    <t>Wow Momo</t>
+  </si>
+  <si>
     <t>Euronet Services</t>
   </si>
   <si>
-    <t>Gvs 3rd Party Offers</t>
-  </si>
-  <si>
     <t>Unipin (india) Private Limited</t>
   </si>
   <si>
     <t>PINE LABS Limited</t>
   </si>
   <si>
+    <t>Grapefruit Payment Solutions Private Limited</t>
+  </si>
+  <si>
     <t>Kochi Metro Rail Limited</t>
   </si>
   <si>
@@ -136,6 +148,9 @@
     <t>Mumbai Metro</t>
   </si>
   <si>
+    <t>Rooter Sports Technologies</t>
+  </si>
+  <si>
     <t>E Xpress Interactive Software PVT LTD</t>
   </si>
   <si>
@@ -151,15 +166,15 @@
     <t>Advance</t>
   </si>
   <si>
-    <t>PFC</t>
-  </si>
-  <si>
     <t>8302745</t>
   </si>
   <si>
     <t>8302749</t>
   </si>
   <si>
+    <t>8302940</t>
+  </si>
+  <si>
     <t>939791</t>
   </si>
   <si>
@@ -175,7 +190,13 @@
     <t>951754</t>
   </si>
   <si>
+    <t>951824</t>
+  </si>
+  <si>
     <t>952151</t>
+  </si>
+  <si>
+    <t>8303195</t>
   </si>
   <si>
     <t>8303163</t>
@@ -519,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -574,19 +595,19 @@
         <v>8302253</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>11931191</v>
+        <v>9808654</v>
       </c>
       <c r="E2">
-        <v>11334275.92</v>
+        <v>9317936.82</v>
       </c>
       <c r="F2">
-        <v>11131941.77</v>
+        <v>9147611.029999999</v>
       </c>
       <c r="G2">
-        <v>202334.77</v>
+        <v>170326.42</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -598,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M2">
         <v>-0</v>
@@ -612,22 +633,22 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>8302697</v>
+        <v>8303177</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>1531161</v>
+        <v>250</v>
       </c>
       <c r="E3">
-        <v>1458433.65</v>
+        <v>191</v>
       </c>
       <c r="F3">
-        <v>1424074.46</v>
+        <v>161.97</v>
       </c>
       <c r="G3">
-        <v>34359.19</v>
+        <v>29.03</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -639,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -653,22 +674,22 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>8303160</v>
+        <v>8302697</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>1109205</v>
       </c>
       <c r="E4">
-        <v>-5.4</v>
+        <v>1057004.18</v>
       </c>
       <c r="F4">
-        <v>-5.4</v>
+        <v>1030966.03</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>26038.15</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -680,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -697,31 +718,31 @@
         <v>8302745</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5">
-        <v>197639</v>
+        <v>518130</v>
       </c>
       <c r="E5">
-        <v>187825.44</v>
+        <v>479245.15</v>
       </c>
       <c r="F5">
-        <v>185560.71</v>
+        <v>468749.98</v>
       </c>
       <c r="G5">
-        <v>2264.73</v>
+        <v>10495.18</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>185560.71</v>
+        <v>468749.98</v>
       </c>
       <c r="K5">
-        <v>2264.73</v>
+        <v>10495.18</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -738,31 +759,31 @@
         <v>8302749</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6">
-        <v>5647290</v>
+        <v>3015496</v>
       </c>
       <c r="E6">
-        <v>5181574.86</v>
+        <v>2757523.58</v>
       </c>
       <c r="F6">
-        <v>4922208.41</v>
+        <v>2610732.1</v>
       </c>
       <c r="G6">
-        <v>259366.71</v>
+        <v>146791.62</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>4922208.41</v>
+        <v>2610732.1</v>
       </c>
       <c r="K6">
-        <v>259366.71</v>
+        <v>146791.62</v>
       </c>
       <c r="L6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -776,34 +797,34 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>939791</v>
+        <v>8302940</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7">
-        <v>19839</v>
+        <v>1000</v>
       </c>
       <c r="E7">
-        <v>19839</v>
+        <v>670</v>
       </c>
       <c r="F7">
-        <v>19839</v>
+        <v>502.5</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>167.5</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>19839</v>
+        <v>502.5</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>167.5</v>
       </c>
       <c r="L7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -817,34 +838,34 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>8303115</v>
+        <v>939791</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D8">
-        <v>4294496</v>
+        <v>17272</v>
       </c>
       <c r="E8">
-        <v>3960876.17</v>
+        <v>17272</v>
       </c>
       <c r="F8">
-        <v>3571162.67</v>
+        <v>17272</v>
       </c>
       <c r="G8">
-        <v>389713.83</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>3571162.67</v>
+        <v>17272</v>
       </c>
       <c r="K8">
-        <v>389713.83</v>
+        <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -858,34 +879,34 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>8303156</v>
+        <v>8303115</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D9">
-        <v>12449</v>
+        <v>5438952</v>
       </c>
       <c r="E9">
-        <v>11488.19</v>
+        <v>5127508.22</v>
       </c>
       <c r="F9">
-        <v>10948</v>
+        <v>4972420.64</v>
       </c>
       <c r="G9">
-        <v>540.1899999999999</v>
+        <v>155088.3</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>10948</v>
+        <v>4972420.64</v>
       </c>
       <c r="K9">
-        <v>540.1900000000001</v>
+        <v>155088.3</v>
       </c>
       <c r="L9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -899,34 +920,34 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>8303155</v>
+        <v>8303156</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10">
-        <v>125635</v>
+        <v>5850</v>
       </c>
       <c r="E10">
-        <v>122329.55</v>
+        <v>5056.15</v>
       </c>
       <c r="F10">
-        <v>122329.55</v>
+        <v>4550.54</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>505.62</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>122329.55</v>
+        <v>4550.54</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>505.62</v>
       </c>
       <c r="L10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -940,19 +961,19 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>951754</v>
+        <v>8303155</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D11">
-        <v>9267.5</v>
+        <v>30705</v>
       </c>
       <c r="E11">
-        <v>9267.5</v>
+        <v>29929.65</v>
       </c>
       <c r="F11">
-        <v>9267.5</v>
+        <v>29929.65</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -961,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>9267.5</v>
+        <v>29929.65</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -981,19 +1002,19 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>952151</v>
+        <v>951754</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D12">
-        <v>610</v>
+        <v>9103.5</v>
       </c>
       <c r="E12">
-        <v>610</v>
+        <v>9103.5</v>
       </c>
       <c r="F12">
-        <v>610</v>
+        <v>9103.5</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1002,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>610</v>
+        <v>9103.5</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1022,34 +1043,34 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>8303163</v>
+        <v>951824</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13">
-        <v>1251000</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>1194757.41</v>
+        <v>120</v>
       </c>
       <c r="F13">
-        <v>1178497.39</v>
+        <v>120</v>
       </c>
       <c r="G13">
-        <v>16260.02</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>1178497.39</v>
+        <v>120</v>
       </c>
       <c r="K13">
-        <v>16260.02</v>
+        <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1063,34 +1084,34 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>8300364</v>
+        <v>952151</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14">
-        <v>2142184</v>
+        <v>26880</v>
       </c>
       <c r="E14">
-        <v>2085426.79</v>
+        <v>26880</v>
       </c>
       <c r="F14">
-        <v>2079605.89</v>
+        <v>26880</v>
       </c>
       <c r="G14">
-        <v>5820.900000000001</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>2079605.89</v>
+        <v>26880</v>
       </c>
       <c r="K14">
-        <v>5820.9</v>
+        <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -1104,34 +1125,34 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>8300503</v>
+        <v>8303195</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15">
-        <v>3000</v>
+        <v>170</v>
       </c>
       <c r="E15">
-        <v>2646</v>
+        <v>159.96</v>
       </c>
       <c r="F15">
-        <v>2513.7</v>
+        <v>159.96</v>
       </c>
       <c r="G15">
-        <v>132.3</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>2513.7</v>
+        <v>159.96</v>
       </c>
       <c r="K15">
-        <v>132.3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -1145,39 +1166,162 @@
         <v>28</v>
       </c>
       <c r="B16">
+        <v>8303163</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16">
+        <v>993000</v>
+      </c>
+      <c r="E16">
+        <v>948356.35</v>
+      </c>
+      <c r="F16">
+        <v>935849.4400000001</v>
+      </c>
+      <c r="G16">
+        <v>12506.91</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>935849.4399999999</v>
+      </c>
+      <c r="K16">
+        <v>12506.91</v>
+      </c>
+      <c r="L16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17">
+        <v>8300364</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17">
+        <v>2590301</v>
+      </c>
+      <c r="E17">
+        <v>2523223.65</v>
+      </c>
+      <c r="F17">
+        <v>2515116</v>
+      </c>
+      <c r="G17">
+        <v>8107.650000000001</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2515116</v>
+      </c>
+      <c r="K17">
+        <v>8107.65</v>
+      </c>
+      <c r="L17" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18">
+        <v>8300503</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18">
+        <v>3867</v>
+      </c>
+      <c r="E18">
+        <v>3410.69</v>
+      </c>
+      <c r="F18">
+        <v>3240.46</v>
+      </c>
+      <c r="G18">
+        <v>170.23</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3240.46</v>
+      </c>
+      <c r="K18">
+        <v>170.23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>63</v>
+      </c>
+      <c r="M18">
+        <v>-0</v>
+      </c>
+      <c r="N18">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19">
         <v>8301652</v>
       </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16">
-        <v>625236</v>
-      </c>
-      <c r="E16">
-        <v>563537.9399999999</v>
-      </c>
-      <c r="F16">
-        <v>531127.7</v>
-      </c>
-      <c r="G16">
-        <v>32410.24</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>531127.7</v>
-      </c>
-      <c r="K16">
-        <v>32410.24</v>
-      </c>
-      <c r="L16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16">
-        <v>-0</v>
-      </c>
-      <c r="N16">
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19">
+        <v>937447</v>
+      </c>
+      <c r="E19">
+        <v>849450.8199999999</v>
+      </c>
+      <c r="F19">
+        <v>803489.53</v>
+      </c>
+      <c r="G19">
+        <v>45961.46</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>803489.53</v>
+      </c>
+      <c r="K19">
+        <v>45961.46</v>
+      </c>
+      <c r="L19" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
         <v>-0</v>
       </c>
     </row>
